--- a/human_validation/judge/kor/judge_D015_S004_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S004_P001__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,208 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 병원에 오시게 된 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 그냥 눈을 뜨지 않으면 아내랑 애들이 더 나을 거라는 생각이 계속 들어요. 저는 또 다른 겨울을 볼 필요가 없다는 말을 계속 하고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 그런 느낌이셨다니 정말 유감입니다. 이런 생각과 느낌이 얼마나 오래 지속됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 볼링 파트너가 죽은 이후부터요... 한 1년 1개월쯤 됐어요. 그때부터 진짜로 시작됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 볼링처럼 예전에 즐기시던 활동에서 흥미나 즐거움을 잃으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 예전엔 브릿지, 정원 일, 교회에서 요리하는 것, 컵스 경기 같은 걸 기대했는데... 지금은 그냥 의자에 앉아만 있어요. 그런 것들에 신경을 쓸 만큼 제 자신을 만들 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지난 1년 전에, 이렇게 우울한 기분을 느낀 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 힘든 시기는 물론 있었지만, 이번처럼 딱 짚을 만한 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 비정상적으로 활력이 넘치거나 세상 꼭대기에 있는 것 같은 느낌, 잠을 거의 필요로 하지 않는 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 그렇게 비정상적으로 활력이 넘치거나 잠을 거의 안 자도 괜찮았던 시기는 기억이 안 나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 지난 1년 동안 수면 상태는 어떠셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 어떻게 대답해야 할지 잘 모르겠어요. 별로 신경 써서 살펴보지 않았던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지난 1년 동안 에너지 수준은 어떠셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 아주 낮아요. 아내는 제가 마치 깊은 눈 속을 걷는 것처럼 움직인다고 해요. 옷을 입거나 부엌을 가로질러 가는 것도 너무 오래 걸려서, 가끔은 다 하지도 못하고 그냥 포기해버려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 지난 1년 동안 식욕이나 체중에 눈에 띄는 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 체중을 제대로 확인해본 적이 없고, 식욕에 큰 변화가 있었다고도 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 집중하거나, 생각을 정리하거나, 일상적인 결정을 내리는 데 어려움을 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네. 시니어센터 예산 숫자를 더 이상 제대로 정리할 수가 없어요. 그리고 청구서나 달력을 30분씩 그냥 쳐다보면서, 제가 뭘 해야 하는지 이해하지 못한 채 앉아 있곤 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>진단명: 정신병적 양상을 동반한 주요우울장애 (D015)
 인구통계: 성별 남성 / 나이 80 / 직업상태 not in workforce / 최종학력 대학 재학
@@ -575,266 +768,42 @@
 증상 지속 기간: None
 추가 요건: delusions_and_hallucinations occur exclusively during the major depressive episode
 주호소 증상 코드: S032
-배경 서술: 제임스의 오랜 볼링 파트너이자 시니어센터 동료 자원봉사자가 갑작스레 세상을 떠나면서, 그의 은퇴 생활을 지탱하고 유용한 사람이라는 느낌을 주던 매주의 일상이 무너졌다. 그 후 1년 1개월에 걸쳐, 그는 브릿지 게임, 정원 가꾸기, 교회 요리 봉사, 컵스 경기 관람에서 물러났고, 눈에 띄게 행동이 느려졌으며, 한때 자랑스럽게 관리하던 예산과 행사 계획도 더 이상 따라갈 수 없게 되었다. 그의 슬픔은 친구를 실망시켰고 벌을 받고 있다는 고정된 믿음으로 굳어졌고, 친구의 목소리를 듣는 생생한 경험, 악화되는 죄책감, 집중력 저하, 자신이 죽으면 가족이 더 나을 거라는 반복적인 생각을 동반했다. 그가 시니어센터에 꾸준히 나오지 않게 되고 '또 다른 겨울을 볼 필요는 없다'는 무서운 말을 한 이후, 그의 아내와 감리교 목사가 그의 1차 진료의를 통해 긴급 정신과 평가를 받을 수 있도록 도왔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 병원에 오시게 된 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 그냥 눈을 뜨지 않으면 아내랑 애들이 더 나을 거라는 생각이 계속 들어요. 저는 또 다른 겨울을 볼 필요가 없다는 말을 계속 하고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 그런 느낌이셨다니 정말 유감입니다. 이런 생각과 느낌이 얼마나 오래 지속됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 볼링 파트너가 죽은 이후부터요... 한 1년 1개월쯤 됐어요. 그때부터 진짜로 시작됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 볼링처럼 예전에 즐기시던 활동에서 흥미나 즐거움을 잃으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 예전엔 브릿지, 정원 일, 교회에서 요리하는 것, 컵스 경기 같은 걸 기대했는데... 지금은 그냥 의자에 앉아만 있어요. 그런 것들에 신경을 쓸 만큼 제 자신을 만들 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지난 1년 전에, 이렇게 우울한 기분을 느낀 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 힘든 시기는 물론 있었지만, 이번처럼 딱 짚을 만한 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 비정상적으로 활력이 넘치거나 세상 꼭대기에 있는 것 같은 느낌, 잠을 거의 필요로 하지 않는 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 그렇게 비정상적으로 활력이 넘치거나 잠을 거의 안 자도 괜찮았던 시기는 기억이 안 나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 지난 1년 동안 수면 상태는 어떠셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 어떻게 대답해야 할지 잘 모르겠어요. 별로 신경 써서 살펴보지 않았던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지난 1년 동안 에너지 수준은 어떠셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 아주 낮아요. 아내는 제가 마치 깊은 눈 속을 걷는 것처럼 움직인다고 해요. 옷을 입거나 부엌을 가로질러 가는 것도 너무 오래 걸려서, 가끔은 다 하지도 못하고 그냥 포기해버려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 지난 1년 동안 식욕이나 체중에 눈에 띄는 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 체중을 제대로 확인해본 적이 없고, 식욕에 큰 변화가 있었다고도 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 집중하거나, 생각을 정리하거나, 일상적인 결정을 내리는 데 어려움을 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네. 시니어센터 예산 숫자를 더 이상 제대로 정리할 수가 없어요. 그리고 청구서나 달력을 30분씩 그냥 쳐다보면서, 제가 뭘 해야 하는지 이해하지 못한 채 앉아 있곤 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+배경 서술: 제임스의 오랜 볼링 파트너이자 시니어센터 동료 자원봉사자가 갑작스레 세상을 떠나면서, 그의 은퇴 생활을 지탱하고 유용한 사람이라는 느낌을 주던 매주의 일상이 무너졌다. 그 후 1년 1개월에 걸쳐, 그는 브릿지 게임, 정원 가꾸기, 교회 요리 봉사, 컵스 경기 관람에서 물러났고, 눈에 띄게 행동이 느려졌으며, 한때 자랑스럽게 관리하던 예산과 행사 계획도 더 이상 따라갈 수 없게 되었다. 그의 슬픔은 친구를 실망시켰고 벌을 받고 있다는 고정된 믿음으로 굳어졌고, 친구의 목소리를 듣는 생생한 경험, 악화되는 죄책감, 집중력 저하, 자신이 죽으면 가족이 더 나을 거라는 반복적인 생각을 동반했다. 그가 시니어센터에 꾸준히 나오지 않게 되고 '또 다른 겨울을 볼 필요는 없다'는 무서운 말을 한 이후, 그의 아내와 감리교 목사가 그의 1차 진료의를 통해 긴급 정신과 평가를 받을 수 있도록 도왔다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D015_S004_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S004_P001__gemini-3.8-flash_kor.xlsx
@@ -754,6 +754,11 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -799,11 +804,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D015_S004_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D015_S004_P001__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.121</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1521</v>
+        <v>0.1926</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5938</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
